--- a/DateBase/orders/Nhat 48_2026-9-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-26.xlsx
@@ -526,6 +526,9 @@
       <c r="C11" t="str">
         <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -584,7 +587,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05211810101010550</v>
+        <v>05211810101010555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -530,9 +530,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>558_油画小菊_Helenium_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>820_蝴蝶洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>360_夕雾草_undefined_Trachelium caeruleum L._1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2</v>
+      </c>
+      <c r="C18" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,7 +667,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05211810101010555</v>
+        <v>0521181010101055510101510510102050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -605,14 +605,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L20"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -667,7 +662,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0521181010101055510101510510102050</v>
+        <v>052118101010105551010151051010205</v>
       </c>
     </row>
   </sheetData>
